--- a/Documentation/LimeAPI_descruption.xlsx
+++ b/Documentation/LimeAPI_descruption.xlsx
@@ -986,23 +986,23 @@
     </xf>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="false"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3" customBuiltin="false"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6" customBuiltin="false"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4" customBuiltin="false"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7" customBuiltin="false"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5" customBuiltin="false"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q67"/>
-  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.93"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.01"/>
@@ -1017,11 +1017,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="3" width="11.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="3" width="16.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="3" width="17.13"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="14" min="14" style="3" width="11.56"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="14" min="14" style="3" width="11.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="3" width="9.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="3" width="16.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="3" width="43.25"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="18" style="0" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4578,7 +4577,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
